--- a/results/profile_output.xlsx
+++ b/results/profile_output.xlsx
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>52.57600000000093</v>
+        <v>52.28800000000047</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -466,7 +466,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>51.19999999999709</v>
+        <v>51.52100000000064</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>50.91200000000026</v>
+        <v>48.54399999999805</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -498,7 +498,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>18.55999999999767</v>
+        <v>18.84799999999814</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>13.44000000000051</v>
+        <v>13.21600000000035</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>963.325</v>
+        <v>1054.472</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.546000000002323</v>
+        <v>9.209000000006654</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>338.5559999999996</v>
+        <v>297.7529999999961</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102.5499999999938</v>
+        <v>105.0510000000086</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7758.975000000009</v>
+        <v>7769.589000000004</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.561000000001513</v>
+        <v>8.629999999997381</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>78.81700000000092</v>
+        <v>80.89599999999882</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>967.0439999999999</v>
+        <v>972.0499999999993</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1403.537</v>
+        <v>1506.759</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.21899999999914</v>
+        <v>15.83799999999974</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.1309999999994</v>
+        <v>22.3739999999998</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>59.90500000002794</v>
+        <v>61.24800000002142</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>476.1780000000144</v>
+        <v>847.4749999999767</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.88000000000466</v>
+        <v>37.98000000003958</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.3629999999539</v>
+        <v>25.50399999995716</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.18199999997159</v>
+        <v>12.2609999999986</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
